--- a/Dealbreak_GameData_IDs_Terminology_Fixed.xlsx
+++ b/Dealbreak_GameData_IDs_Terminology_Fixed.xlsx
@@ -704,7 +704,6 @@
       </c>
       <c r="F2" s="34" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="27" customHeight="1" s="32">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -1333,8 +1332,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="29" customHeight="1" s="32">
       <c r="A30" s="43" t="inlineStr">
         <is>
@@ -1375,7 +1372,7 @@
       </c>
       <c r="B33" s="46" t="inlineStr">
         <is>
-          <t>The asset's id field (its save key) and its path. Legacy file names often differ from the Dealbreak name (Lantern.asset is Scanner). Rows without one have no Unity asset.</t>
+          <t>The asset's id field (its save key) and its path. Since 2026-10-22 asset files and folders carry the Dealbreak names (Assets/Data/Gear/Scanner.asset; higher Gear tiers add the rarity, e.g. ClubAmplifierRare). Rows without one have no Unity asset.</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6742,7 @@
       </c>
       <c r="L2" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/Goblin.asset</t>
+          <t>Assets/Data/Enemies/Scrapper.asset</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6796,7 @@
       </c>
       <c r="L3" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/Thief.asset</t>
+          <t>Assets/Data/Enemies/Pickpocket.asset</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6854,7 @@
       </c>
       <c r="L4" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/Knight.asset</t>
+          <t>Assets/Data/Enemies/SecurityGuard.asset</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6910,7 @@
       </c>
       <c r="L5" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/Brute.asset</t>
+          <t>Assets/Data/Enemies/Heavy.asset</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6966,7 @@
       </c>
       <c r="L6" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/Shieldbearer.asset</t>
+          <t>Assets/Data/Enemies/RiotGuard.asset</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7022,7 @@
       </c>
       <c r="L7" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/WarDrummer.asset</t>
+          <t>Assets/Data/Enemies/HypeMan.asset</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7078,7 @@
       </c>
       <c r="L8" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/Duelist.asset</t>
+          <t>Assets/Data/Enemies/Challenger.asset</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7134,7 @@
       </c>
       <c r="L9" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/GoblinCaptain.asset</t>
+          <t>Assets/Data/Enemies/CrewLeader.asset</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7190,7 @@
       </c>
       <c r="L10" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/RoyalKnight.asset</t>
+          <t>Assets/Data/Enemies/RiotCaptain.asset</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7244,7 @@
       </c>
       <c r="L11" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enemies/MasterThief.asset</t>
+          <t>Assets/Data/Enemies/Ghost.asset</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8645,7 @@
       </c>
       <c r="Q2" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/RetaliationEmblem.asset</t>
+          <t>Assets/Data/Gear/CounterpunchGloves.asset</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8724,7 @@
       </c>
       <c r="Q3" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/RetaliationRare.asset</t>
+          <t>Assets/Data/Gear/CounterpunchGlovesRare.asset</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8807,7 @@
       </c>
       <c r="Q4" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/RetaliationEpic.asset</t>
+          <t>Assets/Data/Gear/CounterpunchGlovesEpic.asset</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8886,7 @@
       </c>
       <c r="Q5" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/LeatherArmor.asset</t>
+          <t>Assets/Data/Gear/StreetJacket.asset</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8965,7 @@
       </c>
       <c r="Q6" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ChainArmor.asset</t>
+          <t>Assets/Data/Gear/TacticalPlating.asset</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9044,7 @@
       </c>
       <c r="Q7" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ClubPower.asset</t>
+          <t>Assets/Data/Gear/ClubAmplifier.asset</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9123,7 @@
       </c>
       <c r="Q8" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ClubRare.asset</t>
+          <t>Assets/Data/Gear/ClubAmplifierRare.asset</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9206,7 @@
       </c>
       <c r="Q9" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ClubEpic.asset</t>
+          <t>Assets/Data/Gear/ClubAmplifierEpic.asset</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9285,7 @@
       </c>
       <c r="Q10" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/AceEmblem.asset</t>
+          <t>Assets/Data/Gear/AceProtocol.asset</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9368,7 @@
       </c>
       <c r="Q11" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/AceRare.asset</t>
+          <t>Assets/Data/Gear/AceProtocolRare.asset</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9447,7 @@
       </c>
       <c r="Q12" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/AceEpic.asset</t>
+          <t>Assets/Data/Gear/AceProtocolEpic.asset</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9526,7 @@
       </c>
       <c r="Q13" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/Sword.asset</t>
+          <t>Assets/Data/Gear/PowerBaton.asset</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9605,7 @@
       </c>
       <c r="Q14" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/Dagger.asset</t>
+          <t>Assets/Data/Gear/Scalpel.asset</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9684,7 @@
       </c>
       <c r="Q15" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/FireEmblem.asset</t>
+          <t>Assets/Data/Gear/Lighter.asset</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9761,7 @@
       </c>
       <c r="Q16" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/DiamondPower.asset</t>
+          <t>Assets/Data/Gear/DiamondDriver.asset</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9840,7 @@
       </c>
       <c r="Q17" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/DiamondRare.asset</t>
+          <t>Assets/Data/Gear/DiamondDriverRare.asset</t>
         </is>
       </c>
     </row>
@@ -9926,7 +9923,7 @@
       </c>
       <c r="Q18" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/DiamondEpic.asset</t>
+          <t>Assets/Data/Gear/DiamondDriverEpic.asset</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10006,7 @@
       </c>
       <c r="Q19" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/WanderersBoots.asset</t>
+          <t>Assets/Data/Gear/CityBoots.asset</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10089,7 @@
       </c>
       <c r="Q20" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HiddenTrail.asset</t>
+          <t>Assets/Data/Gear/DetourPin.asset</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10172,7 @@
       </c>
       <c r="Q21" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/GhostLens.asset</t>
+          <t>Assets/Data/Gear/GhostLens.asset</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10322,7 @@
       </c>
       <c r="Q23" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/Lantern.asset</t>
+          <t>Assets/Data/Gear/Scanner.asset</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10405,7 @@
       </c>
       <c r="Q24" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/WarpathBanner.asset</t>
+          <t>Assets/Data/Gear/VarsityJacket.asset</t>
         </is>
       </c>
     </row>
@@ -10485,7 +10482,7 @@
       </c>
       <c r="Q25" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/Tome.asset</t>
+          <t>Assets/Data/Gear/FieldTablet.asset</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10565,7 @@
       </c>
       <c r="Q26" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/Overflow.asset</t>
+          <t>Assets/Data/Gear/OverflowCanister.asset</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10648,7 @@
       </c>
       <c r="Q27" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/OverflowRare.asset</t>
+          <t>Assets/Data/Gear/OverflowCanisterRare.asset</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10731,7 @@
       </c>
       <c r="Q28" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/OverflowEpic.asset</t>
+          <t>Assets/Data/Gear/OverflowCanisterEpic.asset</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10814,7 @@
       </c>
       <c r="Q29" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/BountyLedger.asset</t>
+          <t>Assets/Data/Gear/BountyHologram.asset</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10897,7 @@
       </c>
       <c r="Q30" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/CashbackToken.asset</t>
+          <t>Assets/Data/Gear/CashbackCard.asset</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10980,7 @@
       </c>
       <c r="Q31" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/GildedBlade.asset</t>
+          <t>Assets/Data/Gear/GoldPistol.asset</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11063,7 @@
       </c>
       <c r="Q32" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/MerchantsBadge.asset</t>
+          <t>Assets/Data/Gear/LoyaltyCard.asset</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11144,7 @@
       </c>
       <c r="Q33" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/MerchantsGift.asset</t>
+          <t>Assets/Data/Gear/LoyaltyGift.asset</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11223,7 @@
       </c>
       <c r="Q34" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/GoldenCompass.asset</t>
+          <t>Assets/Data/Gear/PayoutTracker.asset</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11306,7 @@
       </c>
       <c r="Q35" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/GoldenVault.asset</t>
+          <t>Assets/Data/Gear/SavingsSafe.asset</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11389,7 @@
       </c>
       <c r="Q36" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/TrophyRack.asset</t>
+          <t>Assets/Data/Gear/HeadhunterRifle.asset</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11472,7 @@
       </c>
       <c r="Q37" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ChallengersCrest.asset</t>
+          <t>Assets/Data/Gear/RiotHelmet.asset</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11555,7 @@
       </c>
       <c r="Q38" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HuntersLedger.asset</t>
+          <t>Assets/Data/Gear/NotchedPistol.asset</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11636,7 @@
       </c>
       <c r="Q39" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/Dealbreaker.asset</t>
+          <t>Assets/Data/Gear/Dealbreaker.asset</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11715,7 @@
       </c>
       <c r="Q40" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/GlassCommon.asset</t>
+          <t>Assets/Data/Gear/GlassShard.asset</t>
         </is>
       </c>
     </row>
@@ -11797,7 +11794,7 @@
       </c>
       <c r="Q41" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/GlassRare.asset</t>
+          <t>Assets/Data/Gear/GlassShardRare.asset</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11873,7 @@
       </c>
       <c r="Q42" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/GlassEpic.asset</t>
+          <t>Assets/Data/Gear/GlassShardEpic.asset</t>
         </is>
       </c>
     </row>
@@ -11953,7 +11950,7 @@
       </c>
       <c r="Q43" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ArsenalEmblem.asset</t>
+          <t>Assets/Data/Gear/MemoryCard.asset</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12029,7 @@
       </c>
       <c r="Q44" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ArsenalRare.asset</t>
+          <t>Assets/Data/Gear/MemoryCardRare.asset</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12112,7 @@
       </c>
       <c r="Q45" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ArsenalEpic.asset</t>
+          <t>Assets/Data/Gear/MemoryCardEpic.asset</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12195,7 @@
       </c>
       <c r="Q46" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/KingslayersMark.asset</t>
+          <t>Assets/Data/Gear/SpotterEye.asset</t>
         </is>
       </c>
     </row>
@@ -12281,7 +12278,7 @@
       </c>
       <c r="Q47" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/CrownOfEndurance.asset</t>
+          <t>Assets/Data/Gear/SurvivorsBadge.asset</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12361,7 @@
       </c>
       <c r="Q48" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/FieldMedicsKit.asset</t>
+          <t>Assets/Data/Gear/FirstAidKit.asset</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12440,7 @@
       </c>
       <c r="Q49" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/VictoryDraught.asset</t>
+          <t>Assets/Data/Gear/RecoveryPills.asset</t>
         </is>
       </c>
     </row>
@@ -12522,7 +12519,7 @@
       </c>
       <c r="Q50" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HealingLight.asset</t>
+          <t>Assets/Data/Gear/AutoInjector.asset</t>
         </is>
       </c>
     </row>
@@ -12601,7 +12598,7 @@
       </c>
       <c r="Q51" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HeartPower.asset</t>
+          <t>Assets/Data/Gear/HeartMeds.asset</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12677,7 @@
       </c>
       <c r="Q52" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HeartRare.asset</t>
+          <t>Assets/Data/Gear/HeartMedsRare.asset</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12756,7 @@
       </c>
       <c r="Q53" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HeartEpic.asset</t>
+          <t>Assets/Data/Gear/HeartMedsEpic.asset</t>
         </is>
       </c>
     </row>
@@ -12838,7 +12835,7 @@
       </c>
       <c r="Q54" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/MimicEmblem.asset</t>
+          <t>Assets/Data/Gear/EchoDriver.asset</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12914,7 @@
       </c>
       <c r="Q55" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/MimicEpic.asset</t>
+          <t>Assets/Data/Gear/EchoDriverEpic.asset</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12991,7 @@
       </c>
       <c r="Q56" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/DwarfEmblem.asset</t>
+          <t>Assets/Data/Gear/Lowball.asset</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13070,7 @@
       </c>
       <c r="Q57" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/DwarfRare.asset</t>
+          <t>Assets/Data/Gear/LowballRare.asset</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13149,7 @@
       </c>
       <c r="Q58" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/DwarfEpic.asset</t>
+          <t>Assets/Data/Gear/LowballEpic.asset</t>
         </is>
       </c>
     </row>
@@ -13231,7 +13228,7 @@
       </c>
       <c r="Q59" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ReinforcedSleeves.asset</t>
+          <t>Assets/Data/Gear/CarbonSleeves.asset</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13305,7 @@
       </c>
       <c r="Q60" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/Hammer.asset</t>
+          <t>Assets/Data/Gear/ModBench.asset</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13388,7 @@
       </c>
       <c r="Q61" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HammerRare.asset</t>
+          <t>Assets/Data/Gear/ModBenchRare.asset</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13471,7 @@
       </c>
       <c r="Q62" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/AlchemistsKit.asset</t>
+          <t>Assets/Data/Gear/ModCase.asset</t>
         </is>
       </c>
     </row>
@@ -13553,7 +13550,7 @@
       </c>
       <c r="Q63" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ArtisanTools.asset</t>
+          <t>Assets/Data/Gear/ModdersKit.asset</t>
         </is>
       </c>
     </row>
@@ -13636,7 +13633,7 @@
       </c>
       <c r="Q64" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/RoyalFamilyHeirloom.asset</t>
+          <t>Assets/Data/Gear/NuclearOption.asset</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13712,7 @@
       </c>
       <c r="Q65" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HandsEmblem.asset</t>
+          <t>Assets/Data/Gear/MatchedCells.asset</t>
         </is>
       </c>
     </row>
@@ -13798,7 +13795,7 @@
       </c>
       <c r="Q66" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HandsRare.asset</t>
+          <t>Assets/Data/Gear/MatchedCellsRare.asset</t>
         </is>
       </c>
     </row>
@@ -13877,7 +13874,7 @@
       </c>
       <c r="Q67" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/HandsEpic.asset</t>
+          <t>Assets/Data/Gear/MatchedCellsEpic.asset</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13957,7 @@
       </c>
       <c r="Q68" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/BalancersScale.asset</t>
+          <t>Assets/Data/Gear/FlipSwitch.asset</t>
         </is>
       </c>
     </row>
@@ -14039,7 +14036,7 @@
       </c>
       <c r="Q69" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/SpadePower.asset</t>
+          <t>Assets/Data/Gear/SpadeShield.asset</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14115,7 @@
       </c>
       <c r="Q70" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/SpadeRare.asset</t>
+          <t>Assets/Data/Gear/SpadeShieldRare.asset</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14194,7 @@
       </c>
       <c r="Q71" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/SpadeEpic.asset</t>
+          <t>Assets/Data/Gear/SpadeShieldEpic.asset</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14277,7 @@
       </c>
       <c r="Q72" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/TravelerPackCommon.asset</t>
+          <t>Assets/Data/Gear/CargoCase.asset</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14360,7 @@
       </c>
       <c r="Q73" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/TravelerPackRare.asset</t>
+          <t>Assets/Data/Gear/CargoCaseRare.asset</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14443,7 @@
       </c>
       <c r="Q74" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ScavengersPouch.asset</t>
+          <t>Assets/Data/Gear/GrapplingHook.asset</t>
         </is>
       </c>
     </row>
@@ -14529,7 +14526,7 @@
       </c>
       <c r="Q75" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/PreparationManual.asset</t>
+          <t>Assets/Data/Gear/GuardDrone.asset</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14607,7 @@
       </c>
       <c r="Q76" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/ScavengersSatchel.asset</t>
+          <t>Assets/Data/Gear/SupplyCrate.asset</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14684,7 @@
       </c>
       <c r="Q77" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/CheaterEmblem.asset</t>
+          <t>Assets/Data/Gear/SecondWind.asset</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14765,7 @@
       </c>
       <c r="Q78" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Relics/CheaterRare.asset</t>
+          <t>Assets/Data/Gear/SecondWindRare.asset</t>
         </is>
       </c>
     </row>
@@ -14986,7 +14983,7 @@
       </c>
       <c r="P2" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Sharpened.asset</t>
+          <t>Assets/Data/Mods/Boosted.asset</t>
         </is>
       </c>
     </row>
@@ -15060,7 +15057,7 @@
       </c>
       <c r="P3" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Reinforced.asset</t>
+          <t>Assets/Data/Mods/Plated.asset</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15131,7 @@
       </c>
       <c r="P4" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Mending.asset</t>
+          <t>Assets/Data/Mods/Regenerative.asset</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15205,7 @@
       </c>
       <c r="P5" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Quickdraw.asset</t>
+          <t>Assets/Data/Mods/Quickload.asset</t>
         </is>
       </c>
     </row>
@@ -15286,7 +15283,7 @@
       </c>
       <c r="P6" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Devouring.asset</t>
+          <t>Assets/Data/Mods/Predatory.asset</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15359,7 @@
       </c>
       <c r="P7" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Lethal.asset</t>
+          <t>Assets/Data/Mods/Deadeye.asset</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15433,7 @@
       </c>
       <c r="P8" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Golden.asset</t>
+          <t>Assets/Data/Mods/Profitable.asset</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15507,7 @@
       </c>
       <c r="P9" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Auxiliary.asset</t>
+          <t>Assets/Data/Mods/Backup.asset</t>
         </is>
       </c>
     </row>
@@ -15586,7 +15583,7 @@
       </c>
       <c r="P10" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Explosive.asset</t>
+          <t>Assets/Data/Mods/Volatile.asset</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15659,7 @@
       </c>
       <c r="P11" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Vampiric.asset</t>
+          <t>Assets/Data/Mods/Overclocked.asset</t>
         </is>
       </c>
     </row>
@@ -15738,7 +15735,7 @@
       </c>
       <c r="P12" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/Shifting.asset</t>
+          <t>Assets/Data/Mods/Wildcard.asset</t>
         </is>
       </c>
     </row>
@@ -15818,7 +15815,7 @@
       </c>
       <c r="P13" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Enhancements/DoubleStrike.asset</t>
+          <t>Assets/Data/Mods/DoubleStrike.asset</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16009,7 @@
       </c>
       <c r="N2" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Bread.asset</t>
+          <t>Assets/Data/Tricks/EnergyBar.asset</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16071,7 @@
       </c>
       <c r="N3" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/ThrowingKnife.asset</t>
+          <t>Assets/Data/Tricks/ThrowingStar.asset</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16135,7 @@
       </c>
       <c r="N4" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Whetstone.asset</t>
+          <t>Assets/Data/Tricks/BoosterShot.asset</t>
         </is>
       </c>
     </row>
@@ -16206,7 +16203,7 @@
       </c>
       <c r="N5" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Mirror.asset</t>
+          <t>Assets/Data/Tricks/CloneVial.asset</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16271,7 @@
       </c>
       <c r="N6" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Torch.asset</t>
+          <t>Assets/Data/Tricks/Shears.asset</t>
         </is>
       </c>
     </row>
@@ -16338,7 +16335,7 @@
       </c>
       <c r="N7" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Bomb.asset</t>
+          <t>Assets/Data/Tricks/Firecracker.asset</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16399,7 @@
       </c>
       <c r="N8" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/IronPlate.asset</t>
+          <t>Assets/Data/Tricks/AlloyPlate.asset</t>
         </is>
       </c>
     </row>
@@ -16466,7 +16463,7 @@
       </c>
       <c r="N9" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/NeedleThread.asset</t>
+          <t>Assets/Data/Tricks/Bandage.asset</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16527,7 @@
       </c>
       <c r="N10" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Quiver.asset</t>
+          <t>Assets/Data/Tricks/QuickMarker.asset</t>
         </is>
       </c>
     </row>
@@ -16594,7 +16591,7 @@
       </c>
       <c r="N11" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/SoulStone.asset</t>
+          <t>Assets/Data/Tricks/FeralCapsule.asset</t>
         </is>
       </c>
     </row>
@@ -16658,7 +16655,7 @@
       </c>
       <c r="N12" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Venom.asset</t>
+          <t>Assets/Data/Tricks/LaserScope.asset</t>
         </is>
       </c>
     </row>
@@ -16722,7 +16719,7 @@
       </c>
       <c r="N13" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/MidasCoin.asset</t>
+          <t>Assets/Data/Tricks/PokerChip.asset</t>
         </is>
       </c>
     </row>
@@ -16786,7 +16783,7 @@
       </c>
       <c r="N14" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Talisman.asset</t>
+          <t>Assets/Data/Tricks/BackupDrone.asset</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16847,7 @@
       </c>
       <c r="N15" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/BloodVial.asset</t>
+          <t>Assets/Data/Tricks/BloodBag.asset</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16911,7 @@
       </c>
       <c r="N16" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/Prism.asset</t>
+          <t>Assets/Data/Tricks/PrismCube.asset</t>
         </is>
       </c>
     </row>
@@ -16982,7 +16979,7 @@
       </c>
       <c r="N17" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/SpadeRune.asset</t>
+          <t>Assets/Data/Tricks/SpadeCrystal.asset</t>
         </is>
       </c>
     </row>
@@ -17050,7 +17047,7 @@
       </c>
       <c r="N18" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/HeartRune.asset</t>
+          <t>Assets/Data/Tricks/HeartCrystal.asset</t>
         </is>
       </c>
     </row>
@@ -17118,7 +17115,7 @@
       </c>
       <c r="N19" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/ClubRune.asset</t>
+          <t>Assets/Data/Tricks/ClubCrystal.asset</t>
         </is>
       </c>
     </row>
@@ -17186,7 +17183,7 @@
       </c>
       <c r="N20" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/DiamondRune.asset</t>
+          <t>Assets/Data/Tricks/DiamondCrystal.asset</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17251,7 @@
       </c>
       <c r="N21" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Consumables/DoubleStrikePatch.asset</t>
+          <t>Assets/Data/Tricks/DoubleTap.asset</t>
         </is>
       </c>
     </row>
@@ -17473,7 +17470,7 @@
       </c>
       <c r="P2" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/RoadsideCache.asset</t>
+          <t>Assets/Data/Run/Incidents/DeadDrop.asset</t>
         </is>
       </c>
     </row>
@@ -17551,7 +17548,7 @@
       </c>
       <c r="P3" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/LostCaravan.asset</t>
+          <t>Assets/Data/Run/Incidents/AbandonedDelivery.asset</t>
         </is>
       </c>
     </row>
@@ -17629,7 +17626,7 @@
       </c>
       <c r="P4" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/GamblersShrine.asset</t>
+          <t>Assets/Data/Run/Incidents/RiggedMachine.asset</t>
         </is>
       </c>
     </row>
@@ -17707,7 +17704,7 @@
       </c>
       <c r="P5" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/DangerousShortcut.asset</t>
+          <t>Assets/Data/Run/Incidents/ServiceTunnel.asset</t>
         </is>
       </c>
     </row>
@@ -17785,7 +17782,7 @@
       </c>
       <c r="P6" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/Blacksmith.asset</t>
+          <t>Assets/Data/Run/Incidents/StreetMechanic.asset</t>
         </is>
       </c>
     </row>
@@ -17863,7 +17860,7 @@
       </c>
       <c r="P7" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/Tavern.asset</t>
+          <t>Assets/Data/Run/Incidents/LateNightDiner.asset</t>
         </is>
       </c>
     </row>
@@ -17941,7 +17938,7 @@
       </c>
       <c r="P8" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/Ambush.asset</t>
+          <t>Assets/Data/Run/Incidents/BackAlleyTrap.asset</t>
         </is>
       </c>
     </row>
@@ -18019,7 +18016,7 @@
       </c>
       <c r="P9" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/MysteriousStranger.asset</t>
+          <t>Assets/Data/Run/Incidents/AnonymousContact.asset</t>
         </is>
       </c>
     </row>
@@ -18097,7 +18094,7 @@
       </c>
       <c r="P10" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/NobleFamily.asset</t>
+          <t>Assets/Data/Run/Incidents/VIPParty.asset</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18172,7 @@
       </c>
       <c r="P11" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/Swamp.asset</t>
+          <t>Assets/Data/Run/Incidents/ToxicRunoff.asset</t>
         </is>
       </c>
     </row>
@@ -18257,7 +18254,7 @@
       </c>
       <c r="P12" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/BloodRitual.asset</t>
+          <t>Assets/Data/Run/Incidents/RedlineDeal.asset</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18316,7 @@
       </c>
       <c r="P13" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/FieldLessons.asset</t>
+          <t>Assets/Data/Run/Incidents/CrashCourse.asset</t>
         </is>
       </c>
     </row>
@@ -18381,7 +18378,7 @@
       </c>
       <c r="P14" s="50" t="inlineStr">
         <is>
-          <t>Assets/Data/Run/Events/TrainingGrounds.asset</t>
+          <t>Assets/Data/Run/Incidents/TestLab.asset</t>
         </is>
       </c>
     </row>

--- a/Dealbreak_GameData_IDs_Terminology_Fixed.xlsx
+++ b/Dealbreak_GameData_IDs_Terminology_Fixed.xlsx
@@ -8461,7 +8461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="32" min="1" max="1"/>
@@ -14766,6 +14766,89 @@
       <c r="Q78" s="50" t="inlineStr">
         <is>
           <t>Assets/Data/Gear/SecondWindRare.asset</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="49" t="inlineStr">
+        <is>
+          <t>gear_141</t>
+        </is>
+      </c>
+      <c r="B79" s="49" t="inlineStr">
+        <is>
+          <t>Overclock</t>
+        </is>
+      </c>
+      <c r="C79" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="49" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E79" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="F79" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="49" t="inlineStr">
+        <is>
+          <t>Mod Build</t>
+        </is>
+      </c>
+      <c r="H79" s="49" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="I79" s="49" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="J79" s="50" t="inlineStr">
+        <is>
+          <t>Owned</t>
+        </is>
+      </c>
+      <c r="K79" s="50" t="inlineStr">
+        <is>
+          <t>Every modded card plays its Mod's Signature version: the Signature effects, name and text replace the normal ones.</t>
+        </is>
+      </c>
+      <c r="L79" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="50" t="inlineStr">
+        <is>
+          <t>While owned</t>
+        </is>
+      </c>
+      <c r="N79" s="49" t="inlineStr">
+        <is>
+          <t>Pending Acceptance</t>
+        </is>
+      </c>
+      <c r="O79" s="50" t="inlineStr">
+        <is>
+          <t>In game since 2026-10-24. Owner rule: a Signature changes how the card plays, never just a bigger number. Signatures are in the Mods tab (Signature Name / Signature Effect). Legendary: never sold.</t>
+        </is>
+      </c>
+      <c r="P79" s="49" t="inlineStr">
+        <is>
+          <t>rel_141</t>
+        </is>
+      </c>
+      <c r="Q79" s="50" t="inlineStr">
+        <is>
+          <t>Assets/Data/Gear/Overclock.asset</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="32" min="1" max="1"/>
@@ -14829,6 +14912,8 @@
     <col width="60" customWidth="1" style="32" min="14" max="14"/>
     <col width="18" customWidth="1" style="32" min="15" max="15"/>
     <col width="40" customWidth="1" style="32" min="16" max="16"/>
+    <col width="18" customWidth="1" style="32" min="17" max="17"/>
+    <col width="60" customWidth="1" style="32" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="32">
@@ -14912,6 +14997,16 @@
           <t>Unity Asset</t>
         </is>
       </c>
+      <c r="Q1" s="48" t="inlineStr">
+        <is>
+          <t>Signature Name</t>
+        </is>
+      </c>
+      <c r="R1" s="48" t="inlineStr">
+        <is>
+          <t>Signature Effect (Overclock)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="49" t="inlineStr">
@@ -14986,6 +15081,16 @@
           <t>Assets/Data/Mods/Boosted.asset</t>
         </is>
       </c>
+      <c r="Q2" s="50" t="inlineStr">
+        <is>
+          <t>Afterburner</t>
+        </is>
+      </c>
+      <c r="R2" s="50" t="inlineStr">
+        <is>
+          <t>+5 damage; damage beyond a kill carries over to the next enemy.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="49" t="inlineStr">
@@ -15060,6 +15165,16 @@
           <t>Assets/Data/Mods/Plated.asset</t>
         </is>
       </c>
+      <c r="Q3" s="50" t="inlineStr">
+        <is>
+          <t>Bulwark</t>
+        </is>
+      </c>
+      <c r="R3" s="50" t="inlineStr">
+        <is>
+          <t>+5 Block; a blocking card stays in hand instead of returning to the draw pile, once per enemy turn.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="49" t="inlineStr">
@@ -15134,6 +15249,16 @@
           <t>Assets/Data/Mods/Regenerative.asset</t>
         </is>
       </c>
+      <c r="Q4" s="50" t="inlineStr">
+        <is>
+          <t>Transfusion</t>
+        </is>
+      </c>
+      <c r="R4" s="50" t="inlineStr">
+        <is>
+          <t>While in hand: heal 2 at turn start; healing past full HP gives 1 Shield, at most once per fight.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="49" t="inlineStr">
@@ -15208,6 +15333,16 @@
           <t>Assets/Data/Mods/Quickload.asset</t>
         </is>
       </c>
+      <c r="Q5" s="50" t="inlineStr">
+        <is>
+          <t>Tutor</t>
+        </is>
+      </c>
+      <c r="R5" s="50" t="inlineStr">
+        <is>
+          <t>Draw 1 card; 2 with 3 or fewer cards in hand, 3 with 1 or fewer.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="49" t="inlineStr">
@@ -15286,6 +15421,16 @@
           <t>Assets/Data/Mods/Predatory.asset</t>
         </is>
       </c>
+      <c r="Q6" s="50" t="inlineStr">
+        <is>
+          <t>Feeding Frenzy</t>
+        </is>
+      </c>
+      <c r="R6" s="50" t="inlineStr">
+        <is>
+          <t>On a kill: permanently +1 damage, and the card returns to hand.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="49" t="inlineStr">
@@ -15362,6 +15507,16 @@
           <t>Assets/Data/Mods/Deadeye.asset</t>
         </is>
       </c>
+      <c r="Q7" s="50" t="inlineStr">
+        <is>
+          <t>Executioner</t>
+        </is>
+      </c>
+      <c r="R7" s="50" t="inlineStr">
+        <is>
+          <t>25% crit, always against an enemy below 50% HP; crits deal x3.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="49" t="inlineStr">
@@ -15436,6 +15591,16 @@
           <t>Assets/Data/Mods/Profitable.asset</t>
         </is>
       </c>
+      <c r="Q8" s="50" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="R8" s="50" t="inlineStr">
+        <is>
+          <t>While in hand when a fight is won: 1 Credit per 5 Credits held.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="49" t="inlineStr">
@@ -15510,6 +15675,16 @@
           <t>Assets/Data/Mods/Backup.asset</t>
         </is>
       </c>
+      <c r="Q9" s="50" t="inlineStr">
+        <is>
+          <t>Cover Fire</t>
+        </is>
+      </c>
+      <c r="R9" s="50" t="inlineStr">
+        <is>
+          <t>While in hand: each attack also shoots the weakest other enemy for 3 damage.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="49" t="inlineStr">
@@ -15586,6 +15761,16 @@
           <t>Assets/Data/Mods/Volatile.asset</t>
         </is>
       </c>
+      <c r="Q10" s="50" t="inlineStr">
+        <is>
+          <t>Chain Reaction</t>
+        </is>
+      </c>
+      <c r="R10" s="50" t="inlineStr">
+        <is>
+          <t>Area damage; an enemy the blast defeats explodes too, up to 3 chained blasts.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="49" t="inlineStr">
@@ -15662,6 +15847,16 @@
           <t>Assets/Data/Mods/Overclocked.asset</t>
         </is>
       </c>
+      <c r="Q11" s="50" t="inlineStr">
+        <is>
+          <t>Redline</t>
+        </is>
+      </c>
+      <c r="R11" s="50" t="inlineStr">
+        <is>
+          <t>No HP cost; extra damage equal to missing HP.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="49" t="inlineStr">
@@ -15738,6 +15933,16 @@
           <t>Assets/Data/Mods/Wildcard.asset</t>
         </is>
       </c>
+      <c r="Q12" s="50" t="inlineStr">
+        <is>
+          <t>Joker</t>
+        </is>
+      </c>
+      <c r="R12" s="50" t="inlineStr">
+        <is>
+          <t>Counts as any suit and any rank (Ace pairs, Hands sets, Royal Flush and Gear rank checks).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="49" t="inlineStr">
@@ -15816,6 +16021,16 @@
       <c r="P13" s="50" t="inlineStr">
         <is>
           <t>Assets/Data/Mods/DoubleStrike.asset</t>
+        </is>
+      </c>
+      <c r="Q13" s="50" t="inlineStr">
+        <is>
+          <t>Chain Strike</t>
+        </is>
+      </c>
+      <c r="R13" s="50" t="inlineStr">
+        <is>
+          <t>Hits twice, plus once more for each other Chain Strike card in hand.</t>
         </is>
       </c>
     </row>
